--- a/outputs/Lumpy/Lumpy - Low N_d_report.xlsx
+++ b/outputs/Lumpy/Lumpy - Low N_d_report.xlsx
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.727318427186848</v>
+        <v>9.788104731525785</v>
       </c>
       <c r="E4" t="n">
-        <v>3.206355710520069</v>
+        <v>3.702083691356501</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1999999999999995</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6472025380497815</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.626820052346085</v>
+        <v>8.104332801701224</v>
       </c>
       <c r="E5" t="n">
-        <v>2.946603446874545</v>
+        <v>2.902719290007982</v>
       </c>
       <c r="F5" t="n">
-        <v>5.846715134147404</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8205361365770784</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.200426227052185</v>
+        <v>8.104332801701224</v>
       </c>
       <c r="E6" t="n">
-        <v>2.898703721592327</v>
+        <v>2.902719290007982</v>
       </c>
       <c r="F6" t="n">
-        <v>2.675928598703913</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1651041374277213</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.173013273199524</v>
+        <v>8.104332801701224</v>
       </c>
       <c r="E7" t="n">
-        <v>2.953825124448852</v>
+        <v>2.902719290007982</v>
       </c>
       <c r="F7" t="n">
-        <v>11.40657345797322</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1485937236849492</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.152894295693501</v>
+        <v>8.104332801701224</v>
       </c>
       <c r="E8" t="n">
-        <v>2.957979673491518</v>
+        <v>2.902719290007982</v>
       </c>
       <c r="F8" t="n">
-        <v>11.5659161121759</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6115637685128188</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>7.462803450913531</v>
+        <v>8.104332801701224</v>
       </c>
       <c r="E9" t="n">
-        <v>3.063563097905833</v>
+        <v>2.902719290007982</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7659416101100927</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="10">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>7.365566378066377</v>
+        <v>6.482774170274172</v>
       </c>
       <c r="E12" t="n">
-        <v>3.65367346734714</v>
+        <v>3.159585510735113</v>
       </c>
       <c r="F12" t="n">
-        <v>1.999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.481197006656498</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>8.998373409987638</v>
+        <v>7.152597402597404</v>
       </c>
       <c r="E13" t="n">
-        <v>4.487582481104695</v>
+        <v>3.52131328715778</v>
       </c>
       <c r="F13" t="n">
-        <v>2.628627197904851</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.600000024621712</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>9.588112156096551</v>
+        <v>8.765512265512266</v>
       </c>
       <c r="E14" t="n">
-        <v>4.814520018173258</v>
+        <v>4.344283072552027</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.227987275139763</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4159264931087289</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.282025989014475</v>
+        <v>5.751803751803752</v>
       </c>
       <c r="E15" t="n">
-        <v>4.197542142568642</v>
+        <v>3.042692984782932</v>
       </c>
       <c r="F15" t="n">
-        <v>11.62918706283285</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.374333843797856</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.298330965870604</v>
+        <v>5.751803751803752</v>
       </c>
       <c r="E16" t="n">
-        <v>4.212508566415776</v>
+        <v>3.042692984782932</v>
       </c>
       <c r="F16" t="n">
-        <v>11.76626835654957</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.95030528</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>5.853207264646463</v>
+        <v>5.718253968253969</v>
       </c>
       <c r="E17" t="n">
-        <v>3.070684437303376</v>
+        <v>3.062661290429319</v>
       </c>
       <c r="F17" t="n">
-        <v>4.320542719999998</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8033466584598062</v>
+        <v>0.765092055676006</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.999999865889549</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>10.86666665007803</v>
+        <v>10.2</v>
       </c>
       <c r="E21" t="n">
-        <v>9.72703326717434</v>
+        <v>9.064807317715974</v>
       </c>
       <c r="F21" t="n">
-        <v>2.666666804305047</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.99999965727329</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>11.2166651390059</v>
+        <v>11.55</v>
       </c>
       <c r="E22" t="n">
-        <v>8.96647481875925</v>
+        <v>9.289057291558366</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.333334466858391</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.076923076923077</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.805128205128204</v>
+        <v>9.15</v>
       </c>
       <c r="E23" t="n">
-        <v>9.667472839847383</v>
+        <v>9.001016202792151</v>
       </c>
       <c r="F23" t="n">
-        <v>11.58974358974359</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.969230769230769</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.854615384615384</v>
+        <v>9.15</v>
       </c>
       <c r="E24" t="n">
-        <v>9.701001788733365</v>
+        <v>9.001016202792151</v>
       </c>
       <c r="F24" t="n">
-        <v>11.73076923076923</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>9.119999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="E25" t="n">
-        <v>9.000650383004173</v>
+        <v>9.001016202792151</v>
       </c>
       <c r="F25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
